--- a/docs/03_test/部門削除のテストケース.xlsx
+++ b/docs/03_test/部門削除のテストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F50F25-F8A2-4884-8A9B-9BA355286F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBE8BB0-674C-4A5E-8B61-517319DFB3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>手順No.</t>
     <rPh sb="0" eb="2">
@@ -277,6 +277,124 @@
     </rPh>
     <rPh sb="22" eb="23">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③異常系：社員がいる部署を削除しようとするパターン</t>
+    <rPh sb="1" eb="4">
+      <t>イジョウケイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「社員がいるため削除できません。」とエラーが出る</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「情報システム部」をプルダウンで選択して完了ボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員の選択画面に遷移する</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>センタクガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の部門削除ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>①正常系その1：削除完了後に続けて削除するパターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②正常系その2：削除完了後にメニューに戻るパターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③異常系：社員がいる部署を削除しようとするパターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -285,7 +403,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +415,21 @@
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -324,17 +457,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -344,8 +472,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -359,6 +498,539 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2188579</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>889000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{757E1319-123C-5B5E-CBA4-2656A268E326}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5286375" y="666750"/>
+          <a:ext cx="2188579" cy="889000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>91758</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>810639</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68116D07-BB0E-C32B-CF46-EF4B039A7096}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="1796916"/>
+          <a:ext cx="2293992" cy="810638"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2094149</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>809395</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5239087A-343F-A99D-9D3D-185EAC4AE89C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="2904787"/>
+          <a:ext cx="2094149" cy="809395"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2168927</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>797127</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{565156F3-630F-2907-8E8A-A6E3074D609D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="4012660"/>
+          <a:ext cx="2168927" cy="797127"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1984791</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>986277</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E1712E2-11C7-7A75-860B-77682573512B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="5120532"/>
+          <a:ext cx="1984791" cy="986277"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144127</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>932235</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EA9FEA-776D-E520-69D7-10D4DD505210}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="6228405"/>
+          <a:ext cx="2346361" cy="932234"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2134681</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>864285</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E1166B1-076D-9A13-331D-D65589658462}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="7565957"/>
+          <a:ext cx="2134681" cy="864285"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2139183</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>770107</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{763304F6-FC52-5004-6474-A6FB28053679}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="8565746"/>
+          <a:ext cx="2139183" cy="770106"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1973668</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>959255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E72A7A-B29F-4C5D-0068-612A34A5DF13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296171" y="9565532"/>
+          <a:ext cx="1973667" cy="959255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>27022</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>523725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A81AEBB6-ED35-6E11-7187-19B9E04EE037}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296170" y="10565320"/>
+          <a:ext cx="2229256" cy="523724"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2148193</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>833667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CACBFE3-5633-D42F-235C-475577461C17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296171" y="11794788"/>
+          <a:ext cx="2148192" cy="833666"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2121171</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>65205</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE3D137-9785-1BE5-B6E9-037F00785E93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5296171" y="12727021"/>
+          <a:ext cx="2121170" cy="997439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -624,167 +1296,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="6" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+    <row r="8" spans="1:5" ht="87" customHeight="1">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="36">
-      <c r="A5">
+    <row r="9" spans="1:5" ht="87" customHeight="1">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="87" customHeight="1">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="87" customHeight="1">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="87" customHeight="1">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="87" customHeight="1">
+      <c r="A13">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="78.5" customHeight="1">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="78.5" customHeight="1">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="36">
-      <c r="A6">
+    <row r="17" spans="1:5" ht="78.5" customHeight="1">
+      <c r="A17">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+    <row r="18" spans="1:5" ht="78.5" customHeight="1">
+      <c r="A18">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="73.5" customHeight="1">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="73.5" customHeight="1">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="36">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="36">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:D10"/>
+  <mergeCells count="4">
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E6" location="Sheet1!A1" display="目次に戻る" xr:uid="{43E0DC7D-7366-4024-93D1-74BD17A344CB}"/>
+    <hyperlink ref="E14" location="Sheet1!A1" display="目次に戻る" xr:uid="{949E4FC0-0E2B-4C42-AB48-4BC385C0B408}"/>
+    <hyperlink ref="E19" location="Sheet1!A1" display="目次に戻る" xr:uid="{FA1326B2-EECE-4739-8CAD-806B266443CB}"/>
+    <hyperlink ref="A2" location="Sheet1!A6" display="①正常系その1：削除完了後に続けて削除するパターン" xr:uid="{5152BE08-3F25-499E-A069-F14A67FEE771}"/>
+    <hyperlink ref="A3" location="Sheet1!A14" display="②正常系その2：削除完了後にメニューに戻るパターン" xr:uid="{6933F8AE-94E4-41B9-A504-ECA94755278C}"/>
+    <hyperlink ref="A4" location="Sheet1!A19" display="③異常系：社員がいる部署を削除しようとするパターン" xr:uid="{09B758A6-7C9B-4431-AA48-C54B3579A17D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/03_test/部門削除のテストケース.xlsx
+++ b/docs/03_test/部門削除のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBE8BB0-674C-4A5E-8B61-517319DFB3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2FDBEF-7820-455D-AB1F-9701A1054758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>手順No.</t>
     <rPh sb="0" eb="2">
@@ -68,41 +68,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の従業員削除ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「総務部」をプルダウンで選択して完了ボタンを押す</t>
-    <rPh sb="1" eb="4">
-      <t>ソウムブ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>確認画面に遷移する</t>
     <rPh sb="0" eb="2">
       <t>カクニン</t>
@@ -111,22 +76,6 @@
       <t>ガメン</t>
     </rPh>
     <rPh sb="5" eb="7">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員削除画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -142,35 +91,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>入力値を保持したまま従業員削除画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ニュウリョクチ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホジ</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>ジュウギョウインサクジョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そのまま完了ボタンを押す</t>
-    <rPh sb="4" eb="6">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>削除ボタンを押す</t>
     <rPh sb="0" eb="2">
       <t>サクジョ</t>
@@ -190,38 +110,6 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>続けて削除するボタンを押す</t>
-    <rPh sb="0" eb="1">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①正常系その1：削除完了後に続けて削除するパターン</t>
-    <rPh sb="0" eb="4">
-      <t>マルイチセイジョウケイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カンリョウゴ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -245,58 +133,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メニューに戻るボタンを押す</t>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メニュー画面に戻る</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「営業部」をプルダウンで選択して完了ボタンを押す</t>
-    <rPh sb="1" eb="4">
-      <t>エイギョウブ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>③異常系：社員がいる部署を削除しようとするパターン</t>
-    <rPh sb="1" eb="4">
-      <t>イジョウケイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「社員がいるため削除できません。」とエラーが出る</t>
     <rPh sb="1" eb="3">
       <t>シャイン</t>
@@ -310,39 +146,145 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「情報システム部」をプルダウンで選択して完了ボタンを押す</t>
+    <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>①正常系その1：削除完了後に続けて削除するパターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧から削除したい開発部の削除ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カイハツブ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧に戻るボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①正常系：誰もいない部署を削除する</t>
     <rPh sb="1" eb="3">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②異常系：社員がいる部署を削除しようとするパターン</t>
+    <rPh sb="1" eb="4">
+      <t>イジョウケイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧から削除したい総務部の削除ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ソウムブ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員の選択画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>センタクガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面上部の部門削除ボタンを押す</t>
+    <t>画面上部の部門一覧ボタンを押す</t>
     <rPh sb="0" eb="2">
       <t>ガメン</t>
     </rPh>
@@ -353,7 +295,7 @@
       <t>ブモン</t>
     </rPh>
     <rPh sb="7" eb="9">
-      <t>サクジョ</t>
+      <t>イチラン</t>
     </rPh>
     <rPh sb="13" eb="14">
       <t>オ</t>
@@ -361,40 +303,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
-    <rPh sb="0" eb="2">
-      <t>モクジ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
+    <t>部門一覧に遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="17" eb="19">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
+    <rPh sb="5" eb="7">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>①正常系その1：削除完了後に続けて削除するパターン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>②正常系その2：削除完了後にメニューに戻るパターン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>③異常系：社員がいる部署を削除しようとするパターン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>目次に戻る</t>
-    <rPh sb="0" eb="2">
-      <t>モクジ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -472,16 +389,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -506,21 +423,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2188579</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>889000</xdr:rowOff>
+      <xdr:colOff>2097488</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="15" name="図 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{757E1319-123C-5B5E-CBA4-2656A268E326}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AB88A0A-59D3-16E0-097C-096EA87A9458}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -536,8 +453,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5286375" y="666750"/>
-          <a:ext cx="2188579" cy="889000"/>
+          <a:off x="5289176" y="2726766"/>
+          <a:ext cx="2097488" cy="761999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -550,21 +467,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>91758</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>810639</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1377130</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>986117</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="18" name="図 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68116D07-BB0E-C32B-CF46-EF4B039A7096}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B77BAB8-2F79-802C-F6C0-60D4E90FD922}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -580,8 +497,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="1796916"/>
-          <a:ext cx="2293992" cy="810638"/>
+          <a:off x="5289176" y="1621118"/>
+          <a:ext cx="1377130" cy="986117"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -599,16 +516,60 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2094149</xdr:colOff>
+      <xdr:colOff>1377130</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>809395</xdr:rowOff>
+      <xdr:rowOff>986117</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="19" name="図 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5239087A-343F-A99D-9D3D-185EAC4AE89C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{666A6EC0-238C-4031-B1E9-003CBE3D5ED2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289176" y="3832412"/>
+          <a:ext cx="1377130" cy="986117"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1792942</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1035643</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EFADAD1-E414-8A3D-A68C-DE7926BAA09C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -624,8 +585,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="2904787"/>
-          <a:ext cx="2094149" cy="809395"/>
+          <a:off x="5289176" y="4938059"/>
+          <a:ext cx="1792942" cy="1035643"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -637,22 +598,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2168927</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>797127</xdr:rowOff>
+      <xdr:colOff>1875119</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>985231</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="22" name="図 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{565156F3-630F-2907-8E8A-A6E3074D609D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A92BC0A-F397-0511-EC0B-20C09DE6BDA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -668,8 +629,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="4012660"/>
-          <a:ext cx="2168927" cy="797127"/>
+          <a:off x="5289177" y="6043706"/>
+          <a:ext cx="1875118" cy="985231"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -682,21 +643,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1984791</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>986277</xdr:rowOff>
+      <xdr:colOff>1613648</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>960891</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E1712E2-11C7-7A75-860B-77682573512B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B757635-C48A-5C1D-BA02-3B8923DAD0A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -712,8 +673,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="5120532"/>
-          <a:ext cx="1984791" cy="986277"/>
+          <a:off x="5289176" y="7380941"/>
+          <a:ext cx="1613648" cy="960891"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -726,21 +687,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>144127</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>932235</xdr:rowOff>
+      <xdr:colOff>14942</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>831335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EA9FEA-776D-E520-69D7-10D4DD505210}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C891587D-789A-54AC-9079-78095E1DEE1E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -756,8 +717,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="6228405"/>
-          <a:ext cx="2346361" cy="932234"/>
+          <a:off x="5289176" y="8374529"/>
+          <a:ext cx="2211295" cy="831335"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -770,21 +731,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2134681</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>864285</xdr:rowOff>
+      <xdr:colOff>1949824</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>874229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="25" name="図 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E1166B1-076D-9A13-331D-D65589658462}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4971A5E0-7587-02A1-E775-726FD05C605A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -800,8 +761,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="7565957"/>
-          <a:ext cx="2134681" cy="864285"/>
+          <a:off x="5289176" y="9368119"/>
+          <a:ext cx="1949824" cy="874228"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -813,22 +774,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2139183</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>770107</xdr:rowOff>
+      <xdr:colOff>1524001</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>902117</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
+        <xdr:cNvPr id="27" name="図 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{763304F6-FC52-5004-6474-A6FB28053679}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24DFC5BF-0E2F-17A8-1D5B-4F5608511F0A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -844,184 +805,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5296170" y="8565746"/>
-          <a:ext cx="2139183" cy="770106"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1973668</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>959255</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E72A7A-B29F-4C5D-0068-612A34A5DF13}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5296171" y="9565532"/>
-          <a:ext cx="1973667" cy="959255"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>27022</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>523725</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A81AEBB6-ED35-6E11-7187-19B9E04EE037}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5296170" y="10565320"/>
-          <a:ext cx="2229256" cy="523724"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2148193</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>833667</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CACBFE3-5633-D42F-235C-475577461C17}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5296171" y="11794788"/>
-          <a:ext cx="2148192" cy="833666"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2121171</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>65205</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE3D137-9785-1BE5-B6E9-037F00785E93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5296171" y="12727021"/>
-          <a:ext cx="2121170" cy="997439"/>
+          <a:off x="5289177" y="10361707"/>
+          <a:ext cx="1524000" cy="902116"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1296,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1307,42 +1092,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>25</v>
+      <c r="A1" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="7" t="s">
-        <v>26</v>
+      <c r="A2" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>27</v>
+      <c r="A3" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="7" t="s">
-        <v>29</v>
+      <c r="A6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1364,10 +1147,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="87" customHeight="1">
@@ -1375,10 +1158,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="87" customHeight="1">
@@ -1386,148 +1169,101 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87" customHeight="1">
       <c r="A11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="87" customHeight="1">
       <c r="A12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="87" customHeight="1">
-      <c r="A13">
-        <v>6</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="7" t="s">
-        <v>29</v>
+    <row r="14" spans="1:5" ht="78.5" customHeight="1">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="78.5" customHeight="1">
       <c r="A15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="78.5" customHeight="1">
       <c r="A16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="78.5" customHeight="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="78.5" customHeight="1">
       <c r="A17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="78.5" customHeight="1">
-      <c r="A18">
-        <v>4</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="73.5" customHeight="1">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="73.5" customHeight="1">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="E6" location="Sheet1!A1" display="目次に戻る" xr:uid="{43E0DC7D-7366-4024-93D1-74BD17A344CB}"/>
-    <hyperlink ref="E14" location="Sheet1!A1" display="目次に戻る" xr:uid="{949E4FC0-0E2B-4C42-AB48-4BC385C0B408}"/>
-    <hyperlink ref="E19" location="Sheet1!A1" display="目次に戻る" xr:uid="{FA1326B2-EECE-4739-8CAD-806B266443CB}"/>
+    <hyperlink ref="E13" location="Sheet1!A1" display="目次に戻る" xr:uid="{949E4FC0-0E2B-4C42-AB48-4BC385C0B408}"/>
     <hyperlink ref="A2" location="Sheet1!A6" display="①正常系その1：削除完了後に続けて削除するパターン" xr:uid="{5152BE08-3F25-499E-A069-F14A67FEE771}"/>
-    <hyperlink ref="A3" location="Sheet1!A14" display="②正常系その2：削除完了後にメニューに戻るパターン" xr:uid="{6933F8AE-94E4-41B9-A504-ECA94755278C}"/>
-    <hyperlink ref="A4" location="Sheet1!A19" display="③異常系：社員がいる部署を削除しようとするパターン" xr:uid="{09B758A6-7C9B-4431-AA48-C54B3579A17D}"/>
+    <hyperlink ref="A3" location="Sheet1!A13" display="②異常系：社員がいる部署を削除しようとするパターン" xr:uid="{6933F8AE-94E4-41B9-A504-ECA94755278C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/03_test/部門削除のテストケース.xlsx
+++ b/docs/03_test/部門削除のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2FDBEF-7820-455D-AB1F-9701A1054758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC8508C-3B80-4208-B376-5561B4449948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>手順No.</t>
     <rPh sb="0" eb="2">
@@ -114,25 +114,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>②正常系その2：削除完了後にメニューに戻るパターン</t>
-    <rPh sb="1" eb="3">
-      <t>セイジョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カンリョウゴ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「社員がいるため削除できません。」とエラーが出る</t>
     <rPh sb="1" eb="3">
       <t>シャイン</t>
@@ -176,57 +157,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門一覧に戻る</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門一覧から削除したい開発部の削除ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>カイハツブ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門一覧に戻るボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>①正常系：誰もいない部署を削除する</t>
     <rPh sb="1" eb="3">
       <t>セイジョウ</t>
@@ -262,18 +192,41 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門一覧から削除したい総務部の削除ボタンを押す</t>
+    <t>画面上部の部署一覧ボタンを押す</t>
     <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧に遷移する</t>
     <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧から削除したい開発部の削除ボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
     <rPh sb="6" eb="8">
       <t>サクジョ</t>
     </rPh>
     <rPh sb="11" eb="14">
-      <t>ソウムブ</t>
+      <t>カイハツブ</t>
     </rPh>
     <rPh sb="15" eb="17">
       <t>サクジョ</t>
@@ -284,34 +237,57 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の部門一覧ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門一覧に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
+    <t>部署一覧に戻る</t>
     <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>センイ</t>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧に戻るボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧から削除したい総務部の削除ボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ソウムブ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発部の削除ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>カイハツブ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -423,21 +399,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2097488</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>762000</xdr:rowOff>
+      <xdr:colOff>2107256</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>888999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AB88A0A-59D3-16E0-097C-096EA87A9458}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{562FE204-081A-A197-1220-55D21D2AABE3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -453,8 +429,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289176" y="2726766"/>
-          <a:ext cx="2097488" cy="761999"/>
+          <a:off x="5287818" y="1616364"/>
+          <a:ext cx="2107256" cy="888999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -467,21 +443,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1377130</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>986117</xdr:rowOff>
+      <xdr:colOff>2143139</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>484909</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B77BAB8-2F79-802C-F6C0-60D4E90FD922}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D185A88A-C3BD-D6F8-CA15-DD02A2C61C26}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -497,8 +473,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289176" y="1621118"/>
-          <a:ext cx="1377130" cy="986117"/>
+          <a:off x="5287818" y="2724727"/>
+          <a:ext cx="2143139" cy="484909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -510,22 +486,66 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1985819</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>867591</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F018AFC-259B-900F-D8E0-A752069F8009}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5287819" y="3833092"/>
+          <a:ext cx="1985818" cy="867590"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1377130</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>986117</xdr:rowOff>
+      <xdr:colOff>2143139</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>484909</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{666A6EC0-238C-4031-B1E9-003CBE3D5ED2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F57BE87A-F9E4-4E63-A992-C72894F17F59}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -541,8 +561,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289176" y="3832412"/>
-          <a:ext cx="1377130" cy="986117"/>
+          <a:off x="5287818" y="4941455"/>
+          <a:ext cx="2143139" cy="484909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -554,66 +574,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69273</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>46183</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1792942</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1035643</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>69273</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>689061</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EFADAD1-E414-8A3D-A68C-DE7926BAA09C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5289176" y="4938059"/>
-          <a:ext cx="1792942" cy="1035643"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1875119</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>985231</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A92BC0A-F397-0511-EC0B-20C09DE6BDA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BACC5F62-B2ED-BD66-506D-E8D4E8E00E63}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -629,8 +605,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289177" y="6043706"/>
-          <a:ext cx="1875118" cy="985231"/>
+          <a:off x="5357091" y="6096001"/>
+          <a:ext cx="2193637" cy="642878"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -642,22 +618,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1613648</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>960891</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>158070</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>923637</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B757635-C48A-5C1D-BA02-3B8923DAD0A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6107911-5DD9-B1F0-C716-27A78FA77C48}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -673,8 +649,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289176" y="7380941"/>
-          <a:ext cx="1613648" cy="960891"/>
+          <a:off x="5287819" y="7158183"/>
+          <a:ext cx="2351706" cy="923636"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -688,20 +664,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>14942</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2089727</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>831335</xdr:rowOff>
+      <xdr:rowOff>907423</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C891587D-789A-54AC-9079-78095E1DEE1E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CF2F011-F549-4AA4-B560-DB08C8CF91ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -717,8 +693,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289176" y="8374529"/>
-          <a:ext cx="2211295" cy="831335"/>
+          <a:off x="5287818" y="8497456"/>
+          <a:ext cx="2089727" cy="907422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -732,20 +708,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1949824</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>192684</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>874229</xdr:rowOff>
+      <xdr:rowOff>531091</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4971A5E0-7587-02A1-E775-726FD05C605A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0D95B3B-7790-BD99-7CCF-12F45B23BA3F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -761,8 +737,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289176" y="9368119"/>
-          <a:ext cx="1949824" cy="874228"/>
+          <a:off x="5287818" y="9490364"/>
+          <a:ext cx="2386321" cy="531091"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -774,22 +750,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1524001</xdr:colOff>
+      <xdr:colOff>2124364</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>902117</xdr:rowOff>
+      <xdr:rowOff>574791</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24DFC5BF-0E2F-17A8-1D5B-4F5608511F0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D13F093-1198-DFF1-8516-CA622DB7A873}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -805,8 +781,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289177" y="10361707"/>
-          <a:ext cx="1524000" cy="902116"/>
+          <a:off x="5287818" y="10483273"/>
+          <a:ext cx="2124364" cy="574791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2089727</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>907422</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F83FD7B6-B305-498B-958C-0ECF10DC221B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5287818" y="11476182"/>
+          <a:ext cx="2089727" cy="907422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1081,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1093,17 +1113,17 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1119,13 +1139,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1147,10 +1167,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="87" customHeight="1">
@@ -1158,7 +1178,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
@@ -1172,7 +1192,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87" customHeight="1">
@@ -1180,88 +1200,96 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="87" customHeight="1">
+      <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="87" customHeight="1">
-      <c r="A12">
+    <row r="13" spans="1:5" ht="87" customHeight="1">
+      <c r="A13">
         <v>6</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="78.5" customHeight="1">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="78.5" customHeight="1">
       <c r="A15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="78.5" customHeight="1">
       <c r="A16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="78.5" customHeight="1">
       <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="78.5" customHeight="1">
+      <c r="A18">
         <v>4</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>14</v>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="E6" location="Sheet1!A1" display="目次に戻る" xr:uid="{43E0DC7D-7366-4024-93D1-74BD17A344CB}"/>
-    <hyperlink ref="E13" location="Sheet1!A1" display="目次に戻る" xr:uid="{949E4FC0-0E2B-4C42-AB48-4BC385C0B408}"/>
+    <hyperlink ref="E14" location="Sheet1!A1" display="目次に戻る" xr:uid="{949E4FC0-0E2B-4C42-AB48-4BC385C0B408}"/>
     <hyperlink ref="A2" location="Sheet1!A6" display="①正常系その1：削除完了後に続けて削除するパターン" xr:uid="{5152BE08-3F25-499E-A069-F14A67FEE771}"/>
     <hyperlink ref="A3" location="Sheet1!A13" display="②異常系：社員がいる部署を削除しようとするパターン" xr:uid="{6933F8AE-94E4-41B9-A504-ECA94755278C}"/>
   </hyperlinks>
